--- a/Термодинамика/1.3.3/1.3.3 Data.xlsx
+++ b/Термодинамика/1.3.3/1.3.3 Data.xlsx
@@ -13,48 +13,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t xml:space="preserve">d = 4.1 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d = 5.2 mm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">d = 3 mm </t>
-  </si>
-  <si>
-    <t xml:space="preserve">l = 50 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">l = 70 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">l = 90 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">l = 40.5 cm !!!</t>
-  </si>
-  <si>
-    <t xml:space="preserve">l =30 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">l = 40 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">l = 30 cm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">l = 30 cm !!!</t>
-  </si>
-  <si>
-    <t>v</t>
-  </si>
-  <si>
-    <t>t</t>
-  </si>
-  <si>
-    <t>dp</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+  <si>
+    <t xml:space="preserve">d4 l50 v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4 l50 t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4 l50 dp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4 l70 v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4 l70 t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4 l70 dp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4 l90 v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4 l90 t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4 l90 dp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4 l40.5! v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4 l40.5! t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d4 l40.5! dp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l30 v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l30 t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l30 dp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l40 v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l40 t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l40 dp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l50 v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l50 t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l50 dp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l90 v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l90 t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l90 dp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l40.5! v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l40.5! t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d5 l40.5! dp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d3 l30 v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d3 l30 t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d3 l30 dp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d3 l50 v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d3 l50 t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d3 l50 dp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d3 l30! v</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d3 l30! t</t>
+  </si>
+  <si>
+    <t xml:space="preserve">d3 l30! dp</t>
   </si>
 </sst>
 </file>
@@ -88,11 +154,8 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -606,1006 +669,876 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="M1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="AB1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="2" ht="12.75">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
+      <c r="A2">
+        <v>1754</v>
+      </c>
+      <c r="B2">
+        <v>30.390000000000001</v>
+      </c>
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
+        <v>374</v>
+      </c>
+      <c r="E2">
+        <v>14.94</v>
+      </c>
+      <c r="F2">
         <v>5</v>
       </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-      <c r="S2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="T2" s="1"/>
-      <c r="U2" s="1"/>
-      <c r="V2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="W2" s="1"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
-      <c r="AB2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC2" s="1"/>
-      <c r="AD2" s="1"/>
-      <c r="AE2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AF2" s="1"/>
-      <c r="AG2" s="1"/>
-      <c r="AH2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="AI2" s="1"/>
-      <c r="AJ2" s="1"/>
+      <c r="G2">
+        <v>344</v>
+      </c>
+      <c r="H2">
+        <v>9.0399999999999991</v>
+      </c>
+      <c r="I2">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="J2">
+        <v>583</v>
+      </c>
+      <c r="K2">
+        <v>9.6799999999999997</v>
+      </c>
+      <c r="L2">
+        <v>11.199999999999999</v>
+      </c>
+      <c r="M2">
+        <v>1503</v>
+      </c>
+      <c r="N2">
+        <v>17.050000000000001</v>
+      </c>
+      <c r="O2">
+        <v>2</v>
+      </c>
+      <c r="P2">
+        <v>550</v>
+      </c>
+      <c r="Q2">
+        <v>6.5599999999999996</v>
+      </c>
+      <c r="R2">
+        <v>2.3999999999999999</v>
+      </c>
+      <c r="S2">
+        <v>606</v>
+      </c>
+      <c r="T2">
+        <v>3.6800000000000002</v>
+      </c>
+      <c r="U2">
+        <v>8.5999999999999996</v>
+      </c>
+      <c r="V2">
+        <v>543</v>
+      </c>
+      <c r="W2">
+        <v>10.380000000000001</v>
+      </c>
+      <c r="X2">
+        <v>3.2000000000000002</v>
+      </c>
+      <c r="Y2">
+        <v>516</v>
+      </c>
+      <c r="Z2">
+        <v>15.06</v>
+      </c>
+      <c r="AA2">
+        <v>1.3999999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>566</v>
+      </c>
+      <c r="AC2">
+        <v>6.29</v>
+      </c>
+      <c r="AD2">
+        <v>12.800000000000001</v>
+      </c>
+      <c r="AE2">
+        <v>543</v>
+      </c>
+      <c r="AF2">
+        <v>10.890000000000001</v>
+      </c>
+      <c r="AG2">
+        <v>9.4000000000000004</v>
+      </c>
+      <c r="AH2">
+        <v>276</v>
+      </c>
+      <c r="AI2">
+        <v>5.3600000000000003</v>
+      </c>
+      <c r="AJ2">
+        <v>9.8000000000000007</v>
+      </c>
     </row>
     <row r="3" ht="12.75">
-      <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="M3" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" t="s">
-        <v>12</v>
-      </c>
-      <c r="O3" t="s">
-        <v>13</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>11</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>12</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>13</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>13</v>
+      <c r="A3">
+        <v>1138</v>
+      </c>
+      <c r="B3">
+        <v>10.27</v>
+      </c>
+      <c r="C3">
+        <v>21.600000000000001</v>
+      </c>
+      <c r="D3">
+        <v>439</v>
+      </c>
+      <c r="E3">
+        <v>6.5800000000000001</v>
+      </c>
+      <c r="F3">
+        <v>14</v>
+      </c>
+      <c r="G3">
+        <v>438</v>
+      </c>
+      <c r="H3">
+        <v>6.7400000000000002</v>
+      </c>
+      <c r="I3">
+        <v>17.699999999999999</v>
+      </c>
+      <c r="J3">
+        <v>603</v>
+      </c>
+      <c r="K3">
+        <v>6.7699999999999996</v>
+      </c>
+      <c r="L3">
+        <v>21</v>
+      </c>
+      <c r="M3">
+        <v>1554</v>
+      </c>
+      <c r="N3">
+        <v>10.029999999999999</v>
+      </c>
+      <c r="O3">
+        <v>4</v>
+      </c>
+      <c r="P3">
+        <v>604</v>
+      </c>
+      <c r="Q3">
+        <v>3.7999999999999998</v>
+      </c>
+      <c r="R3">
+        <v>6.4000000000000004</v>
+      </c>
+      <c r="S3">
+        <v>811</v>
+      </c>
+      <c r="T3">
+        <v>3.5099999999999998</v>
+      </c>
+      <c r="U3">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="V3">
+        <v>779</v>
+      </c>
+      <c r="W3">
+        <v>6.5</v>
+      </c>
+      <c r="X3">
+        <v>7.7999999999999998</v>
+      </c>
+      <c r="Y3">
+        <v>545</v>
+      </c>
+      <c r="Z3">
+        <v>7.2800000000000002</v>
+      </c>
+      <c r="AA3">
+        <v>4</v>
+      </c>
+      <c r="AB3">
+        <v>715</v>
+      </c>
+      <c r="AC3">
+        <v>5.4299999999999997</v>
+      </c>
+      <c r="AD3">
+        <v>28</v>
+      </c>
+      <c r="AE3">
+        <v>592</v>
+      </c>
+      <c r="AF3">
+        <v>6.9699999999999998</v>
+      </c>
+      <c r="AG3">
+        <v>18</v>
+      </c>
+      <c r="AH3">
+        <v>563</v>
+      </c>
+      <c r="AI3">
+        <v>7.7300000000000004</v>
+      </c>
+      <c r="AJ3">
+        <v>18.399999999999999</v>
       </c>
     </row>
     <row r="4" ht="12.75">
       <c r="A4">
-        <v>1754</v>
+        <v>1361</v>
       </c>
       <c r="B4">
-        <v>30.390000000000001</v>
+        <v>8.9900000000000002</v>
       </c>
       <c r="C4">
-        <v>8</v>
+        <v>41.799999999999997</v>
       </c>
       <c r="D4">
-        <v>374</v>
+        <v>585</v>
       </c>
       <c r="E4">
-        <v>14.94</v>
+        <v>6.1299999999999999</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>23.399999999999999</v>
       </c>
       <c r="G4">
-        <v>344</v>
+        <v>1055</v>
       </c>
       <c r="H4">
-        <v>9.0399999999999991</v>
+        <v>10.890000000000001</v>
       </c>
       <c r="I4">
-        <v>9.3000000000000007</v>
+        <v>28.5</v>
       </c>
       <c r="J4">
-        <v>583</v>
+        <v>635</v>
       </c>
       <c r="K4">
-        <v>9.6799999999999997</v>
+        <v>5.6100000000000003</v>
       </c>
       <c r="L4">
-        <v>11.199999999999999</v>
+        <v>33</v>
       </c>
       <c r="M4">
-        <v>1503</v>
+        <v>1510</v>
       </c>
       <c r="N4">
-        <v>17.050000000000001</v>
+        <v>8.3399999999999999</v>
       </c>
       <c r="O4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>550</v>
+        <v>693</v>
       </c>
       <c r="Q4">
-        <v>6.5599999999999996</v>
+        <v>3.6200000000000001</v>
       </c>
       <c r="R4">
-        <v>2.3999999999999999</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>606</v>
+        <v>642</v>
       </c>
       <c r="T4">
-        <v>3.6800000000000002</v>
+        <v>2.3599999999999999</v>
       </c>
       <c r="U4">
-        <v>8.5999999999999996</v>
+        <v>24</v>
       </c>
       <c r="V4">
-        <v>543</v>
+        <v>669</v>
       </c>
       <c r="W4">
-        <v>10.380000000000001</v>
+        <v>4.4199999999999999</v>
       </c>
       <c r="X4">
-        <v>3.2000000000000002</v>
+        <v>12.4</v>
       </c>
       <c r="Y4">
-        <v>516</v>
+        <v>644</v>
       </c>
       <c r="Z4">
-        <v>15.06</v>
+        <v>6.46</v>
       </c>
       <c r="AA4">
-        <v>1.3999999999999999</v>
+        <v>6</v>
       </c>
       <c r="AB4">
-        <v>566</v>
+        <v>795</v>
       </c>
       <c r="AC4">
-        <v>6.29</v>
+        <v>4.9199999999999999</v>
       </c>
       <c r="AD4">
-        <v>12.800000000000001</v>
+        <v>41</v>
       </c>
       <c r="AE4">
-        <v>543</v>
+        <v>595</v>
       </c>
       <c r="AF4">
-        <v>10.890000000000001</v>
+        <v>5.7000000000000002</v>
       </c>
       <c r="AG4">
-        <v>9.4000000000000004</v>
+        <v>29</v>
       </c>
       <c r="AH4">
-        <v>276</v>
+        <v>591</v>
       </c>
       <c r="AI4">
-        <v>5.3600000000000003</v>
+        <v>6.4900000000000002</v>
       </c>
       <c r="AJ4">
-        <v>9.8000000000000007</v>
+        <v>26.600000000000001</v>
       </c>
     </row>
     <row r="5" ht="12.75">
       <c r="A5">
-        <v>1138</v>
+        <v>1192</v>
       </c>
       <c r="B5">
-        <v>10.27</v>
+        <v>6.8300000000000001</v>
       </c>
       <c r="C5">
-        <v>21.600000000000001</v>
+        <v>55.200000000000003</v>
       </c>
       <c r="D5">
-        <v>439</v>
+        <v>655</v>
       </c>
       <c r="E5">
-        <v>6.5800000000000001</v>
+        <v>5.96</v>
       </c>
       <c r="F5">
+        <v>33</v>
+      </c>
+      <c r="G5">
+        <v>486</v>
+      </c>
+      <c r="H5">
+        <v>4.5800000000000001</v>
+      </c>
+      <c r="I5">
+        <v>35.700000000000003</v>
+      </c>
+      <c r="J5">
+        <v>620</v>
+      </c>
+      <c r="K5">
+        <v>4.6699999999999999</v>
+      </c>
+      <c r="L5">
+        <v>46</v>
+      </c>
+      <c r="M5">
+        <v>1804</v>
+      </c>
+      <c r="N5">
+        <v>8.6400000000000006</v>
+      </c>
+      <c r="O5">
+        <v>8</v>
+      </c>
+      <c r="P5">
+        <v>1130</v>
+      </c>
+      <c r="Q5">
+        <v>4.8799999999999999</v>
+      </c>
+      <c r="R5">
         <v>14</v>
       </c>
-      <c r="G5">
-        <v>438</v>
-      </c>
-      <c r="H5">
-        <v>6.7400000000000002</v>
-      </c>
-      <c r="I5">
-        <v>17.699999999999999</v>
-      </c>
-      <c r="J5">
-        <v>603</v>
-      </c>
-      <c r="K5">
-        <v>6.7699999999999996</v>
-      </c>
-      <c r="L5">
-        <v>21</v>
-      </c>
-      <c r="M5">
-        <v>1554</v>
-      </c>
-      <c r="N5">
-        <v>10.029999999999999</v>
-      </c>
-      <c r="O5">
-        <v>4</v>
-      </c>
-      <c r="P5">
-        <v>604</v>
-      </c>
-      <c r="Q5">
-        <v>3.7999999999999998</v>
-      </c>
-      <c r="R5">
-        <v>6.4000000000000004</v>
-      </c>
       <c r="S5">
-        <v>811</v>
+        <v>1179</v>
       </c>
       <c r="T5">
-        <v>3.5099999999999998</v>
+        <v>4.0099999999999998</v>
       </c>
       <c r="U5">
-        <v>17.600000000000001</v>
+        <v>27.800000000000001</v>
       </c>
       <c r="V5">
-        <v>779</v>
+        <v>884</v>
       </c>
       <c r="W5">
-        <v>6.5</v>
+        <v>4.8799999999999999</v>
       </c>
       <c r="X5">
-        <v>7.7999999999999998</v>
+        <v>20</v>
       </c>
       <c r="Y5">
-        <v>545</v>
+        <v>740</v>
       </c>
       <c r="Z5">
-        <v>7.2800000000000002</v>
+        <v>6.1799999999999997</v>
       </c>
       <c r="AA5">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AB5">
-        <v>715</v>
+        <v>826</v>
       </c>
       <c r="AC5">
-        <v>5.4299999999999997</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="AD5">
-        <v>28</v>
+        <v>54.799999999999997</v>
       </c>
       <c r="AE5">
+        <v>616</v>
+      </c>
+      <c r="AF5">
+        <v>4.9299999999999997</v>
+      </c>
+      <c r="AG5">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="AH5">
         <v>592</v>
       </c>
-      <c r="AF5">
-        <v>6.9699999999999998</v>
-      </c>
-      <c r="AG5">
-        <v>18</v>
-      </c>
-      <c r="AH5">
-        <v>563</v>
-      </c>
       <c r="AI5">
-        <v>7.7300000000000004</v>
+        <v>5.7599999999999998</v>
       </c>
       <c r="AJ5">
-        <v>18.399999999999999</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" ht="12.75">
       <c r="A6">
-        <v>1361</v>
+        <v>1388</v>
       </c>
       <c r="B6">
-        <v>8.9900000000000002</v>
+        <v>6.5700000000000003</v>
       </c>
       <c r="C6">
-        <v>41.799999999999997</v>
+        <v>76.799999999999997</v>
       </c>
       <c r="D6">
-        <v>585</v>
+        <v>683</v>
       </c>
       <c r="E6">
-        <v>6.1299999999999999</v>
+        <v>5.6100000000000003</v>
       </c>
       <c r="F6">
-        <v>23.399999999999999</v>
+        <v>43</v>
       </c>
       <c r="G6">
-        <v>1055</v>
+        <v>569</v>
       </c>
       <c r="H6">
-        <v>10.890000000000001</v>
+        <v>4.96</v>
       </c>
       <c r="I6">
-        <v>28.5</v>
+        <v>45</v>
       </c>
       <c r="J6">
-        <v>635</v>
+        <v>683</v>
       </c>
       <c r="K6">
-        <v>5.6100000000000003</v>
+        <v>4.3799999999999999</v>
       </c>
       <c r="L6">
-        <v>33</v>
+        <v>61.5</v>
       </c>
       <c r="M6">
-        <v>1510</v>
+        <v>1250</v>
       </c>
       <c r="N6">
-        <v>8.3399999999999999</v>
+        <v>5.3200000000000003</v>
       </c>
       <c r="O6">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>693</v>
+        <v>1088</v>
       </c>
       <c r="Q6">
-        <v>3.6200000000000001</v>
+        <v>4.1299999999999999</v>
       </c>
       <c r="R6">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="S6">
-        <v>642</v>
+        <v>691</v>
       </c>
       <c r="T6">
-        <v>2.3599999999999999</v>
+        <v>3.6400000000000001</v>
       </c>
       <c r="U6">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="V6">
-        <v>669</v>
+        <v>948</v>
       </c>
       <c r="W6">
-        <v>4.4199999999999999</v>
+        <v>4.46</v>
       </c>
       <c r="X6">
-        <v>12.4</v>
+        <v>27.199999999999999</v>
       </c>
       <c r="Y6">
-        <v>644</v>
+        <v>621</v>
       </c>
       <c r="Z6">
-        <v>6.46</v>
+        <v>4.3600000000000003</v>
       </c>
       <c r="AA6">
-        <v>6</v>
+        <v>10.4</v>
       </c>
       <c r="AB6">
-        <v>795</v>
+        <v>937</v>
       </c>
       <c r="AC6">
-        <v>4.9199999999999999</v>
+        <v>4.4100000000000001</v>
       </c>
       <c r="AD6">
-        <v>41</v>
+        <v>68.400000000000006</v>
       </c>
       <c r="AE6">
-        <v>595</v>
+        <v>761</v>
       </c>
       <c r="AF6">
-        <v>5.7000000000000002</v>
+        <v>5.4900000000000002</v>
       </c>
       <c r="AG6">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="AH6">
-        <v>591</v>
+        <v>578</v>
       </c>
       <c r="AI6">
-        <v>6.4900000000000002</v>
+        <v>4.9100000000000001</v>
       </c>
       <c r="AJ6">
-        <v>26.600000000000001</v>
+        <v>43.600000000000001</v>
       </c>
     </row>
     <row r="7" ht="12.75">
       <c r="A7">
-        <v>1192</v>
+        <v>1660</v>
       </c>
       <c r="B7">
-        <v>6.8300000000000001</v>
+        <v>6.8899999999999997</v>
       </c>
       <c r="C7">
-        <v>55.200000000000003</v>
+        <v>98</v>
       </c>
       <c r="D7">
-        <v>655</v>
+        <v>744</v>
       </c>
       <c r="E7">
-        <v>5.96</v>
+        <v>5.1200000000000001</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>58.799999999999997</v>
       </c>
       <c r="G7">
-        <v>486</v>
+        <v>979</v>
       </c>
       <c r="H7">
-        <v>4.5800000000000001</v>
+        <v>7.6900000000000004</v>
       </c>
       <c r="I7">
-        <v>35.700000000000003</v>
+        <v>54.299999999999997</v>
       </c>
       <c r="J7">
-        <v>620</v>
+        <v>712</v>
       </c>
       <c r="K7">
-        <v>4.6699999999999999</v>
+        <v>4.0099999999999998</v>
       </c>
       <c r="L7">
-        <v>46</v>
+        <v>79.200000000000003</v>
       </c>
       <c r="M7">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="N7">
-        <v>8.6400000000000006</v>
+        <v>6.8700000000000001</v>
       </c>
       <c r="O7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P7">
-        <v>1130</v>
+        <v>1314</v>
       </c>
       <c r="Q7">
-        <v>4.8799999999999999</v>
+        <v>4.5499999999999998</v>
       </c>
       <c r="R7">
-        <v>14</v>
+        <v>21.600000000000001</v>
       </c>
       <c r="S7">
-        <v>1179</v>
+        <v>915</v>
       </c>
       <c r="T7">
-        <v>4.0099999999999998</v>
+        <v>3.7200000000000002</v>
       </c>
       <c r="U7">
-        <v>27.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="V7">
-        <v>884</v>
+        <v>974</v>
       </c>
       <c r="W7">
-        <v>4.8799999999999999</v>
+        <v>4.2400000000000002</v>
       </c>
       <c r="X7">
-        <v>20</v>
+        <v>31.399999999999999</v>
       </c>
       <c r="Y7">
-        <v>740</v>
+        <v>1155</v>
       </c>
       <c r="Z7">
-        <v>6.1799999999999997</v>
+        <v>5.5599999999999996</v>
       </c>
       <c r="AA7">
-        <v>8</v>
+        <v>20.800000000000001</v>
       </c>
       <c r="AB7">
-        <v>826</v>
+        <v>1502</v>
       </c>
       <c r="AC7">
-        <v>4.3600000000000003</v>
+        <v>8.5800000000000001</v>
       </c>
       <c r="AD7">
-        <v>54.799999999999997</v>
+        <v>47.399999999999999</v>
       </c>
       <c r="AE7">
-        <v>616</v>
+        <v>718</v>
       </c>
       <c r="AF7">
-        <v>4.9299999999999997</v>
+        <v>4.5700000000000003</v>
       </c>
       <c r="AG7">
-        <v>40.799999999999997</v>
+        <v>62.399999999999999</v>
       </c>
       <c r="AH7">
-        <v>592</v>
+        <v>630</v>
       </c>
       <c r="AI7">
-        <v>5.7599999999999998</v>
+        <v>4.7300000000000004</v>
       </c>
       <c r="AJ7">
-        <v>34</v>
+        <v>52.200000000000003</v>
       </c>
     </row>
     <row r="8" ht="12.75">
       <c r="A8">
-        <v>1388</v>
+        <v>1367</v>
       </c>
       <c r="B8">
-        <v>6.5700000000000003</v>
+        <v>6.7699999999999996</v>
       </c>
       <c r="C8">
-        <v>76.799999999999997</v>
+        <v>71.400000000000006</v>
       </c>
       <c r="D8">
-        <v>683</v>
+        <v>756</v>
       </c>
       <c r="E8">
-        <v>5.6100000000000003</v>
+        <v>4.46</v>
       </c>
       <c r="F8">
-        <v>43</v>
+        <v>79.5</v>
       </c>
       <c r="G8">
-        <v>569</v>
+        <v>994</v>
       </c>
       <c r="H8">
-        <v>4.96</v>
+        <v>6.71</v>
       </c>
       <c r="I8">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="J8">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="K8">
-        <v>4.3799999999999999</v>
+        <v>3.5099999999999998</v>
       </c>
       <c r="L8">
-        <v>61.5</v>
-      </c>
-      <c r="M8">
-        <v>1250</v>
-      </c>
-      <c r="N8">
-        <v>5.3200000000000003</v>
-      </c>
-      <c r="O8">
-        <v>10</v>
+        <v>94.799999999999997</v>
       </c>
       <c r="P8">
-        <v>1088</v>
+        <v>960</v>
       </c>
       <c r="Q8">
-        <v>4.1299999999999999</v>
+        <v>3.8799999999999999</v>
       </c>
       <c r="R8">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S8">
-        <v>691</v>
+        <v>713</v>
       </c>
       <c r="T8">
-        <v>3.6400000000000001</v>
+        <v>5.46</v>
       </c>
       <c r="U8">
-        <v>12</v>
+        <v>4.7999999999999998</v>
       </c>
       <c r="V8">
-        <v>948</v>
+        <v>1110</v>
       </c>
       <c r="W8">
-        <v>4.46</v>
+        <v>4.4199999999999999</v>
       </c>
       <c r="X8">
-        <v>27.199999999999999</v>
+        <v>37.399999999999999</v>
       </c>
       <c r="Y8">
-        <v>621</v>
+        <v>1490</v>
       </c>
       <c r="Z8">
-        <v>4.3600000000000003</v>
+        <v>5.4000000000000004</v>
       </c>
       <c r="AA8">
-        <v>10.4</v>
+        <v>35.200000000000003</v>
       </c>
       <c r="AB8">
-        <v>937</v>
+        <v>622</v>
       </c>
       <c r="AC8">
-        <v>4.4100000000000001</v>
+        <v>5.7800000000000002</v>
       </c>
       <c r="AD8">
-        <v>68.400000000000006</v>
+        <v>19.199999999999999</v>
       </c>
       <c r="AE8">
-        <v>761</v>
+        <v>847</v>
       </c>
       <c r="AF8">
-        <v>5.4900000000000002</v>
+        <v>4.6299999999999999</v>
       </c>
       <c r="AG8">
-        <v>49</v>
+        <v>81.299999999999997</v>
       </c>
       <c r="AH8">
-        <v>578</v>
+        <v>669</v>
       </c>
       <c r="AI8">
-        <v>4.9100000000000001</v>
+        <v>4.3300000000000001</v>
       </c>
       <c r="AJ8">
-        <v>43.600000000000001</v>
+        <v>69</v>
       </c>
     </row>
-    <row r="9" ht="12.75">
-      <c r="A9">
-        <v>1660</v>
-      </c>
-      <c r="B9">
-        <v>6.8899999999999997</v>
-      </c>
-      <c r="C9">
-        <v>98</v>
-      </c>
-      <c r="D9">
-        <v>744</v>
-      </c>
-      <c r="E9">
-        <v>5.1200000000000001</v>
-      </c>
-      <c r="F9">
-        <v>58.799999999999997</v>
-      </c>
-      <c r="G9">
-        <v>979</v>
-      </c>
-      <c r="H9">
-        <v>7.6900000000000004</v>
-      </c>
-      <c r="I9">
-        <v>54.299999999999997</v>
-      </c>
-      <c r="J9">
-        <v>712</v>
-      </c>
-      <c r="K9">
-        <v>4.0099999999999998</v>
-      </c>
-      <c r="L9">
-        <v>79.200000000000003</v>
-      </c>
-      <c r="M9">
-        <v>1812</v>
-      </c>
-      <c r="N9">
-        <v>6.8700000000000001</v>
-      </c>
-      <c r="O9">
-        <v>12</v>
-      </c>
-      <c r="P9">
-        <v>1314</v>
-      </c>
-      <c r="Q9">
-        <v>4.5499999999999998</v>
-      </c>
-      <c r="R9">
-        <v>21.600000000000001</v>
-      </c>
-      <c r="S9">
-        <v>915</v>
-      </c>
-      <c r="T9">
-        <v>3.7200000000000002</v>
-      </c>
-      <c r="U9">
-        <v>20</v>
-      </c>
-      <c r="V9">
-        <v>974</v>
-      </c>
-      <c r="W9">
-        <v>4.2400000000000002</v>
-      </c>
-      <c r="X9">
-        <v>31.399999999999999</v>
-      </c>
-      <c r="Y9">
-        <v>1155</v>
-      </c>
-      <c r="Z9">
-        <v>5.5599999999999996</v>
-      </c>
-      <c r="AA9">
-        <v>20.800000000000001</v>
-      </c>
-      <c r="AB9">
-        <v>1502</v>
-      </c>
-      <c r="AC9">
-        <v>8.5800000000000001</v>
-      </c>
-      <c r="AD9">
-        <v>47.399999999999999</v>
-      </c>
-      <c r="AE9">
-        <v>718</v>
-      </c>
-      <c r="AF9">
-        <v>4.5700000000000003</v>
-      </c>
-      <c r="AG9">
-        <v>62.399999999999999</v>
-      </c>
-      <c r="AH9">
-        <v>630</v>
-      </c>
-      <c r="AI9">
-        <v>4.7300000000000004</v>
-      </c>
-      <c r="AJ9">
-        <v>52.200000000000003</v>
-      </c>
-    </row>
-    <row r="10" ht="12.75">
-      <c r="A10">
-        <v>1367</v>
-      </c>
-      <c r="B10">
-        <v>6.7699999999999996</v>
-      </c>
-      <c r="C10">
-        <v>71.400000000000006</v>
-      </c>
-      <c r="D10">
-        <v>756</v>
-      </c>
-      <c r="E10">
-        <v>4.46</v>
-      </c>
-      <c r="F10">
-        <v>79.5</v>
-      </c>
-      <c r="G10">
-        <v>994</v>
-      </c>
-      <c r="H10">
-        <v>6.71</v>
-      </c>
-      <c r="I10">
-        <v>72</v>
-      </c>
-      <c r="J10">
-        <v>686</v>
-      </c>
-      <c r="K10">
-        <v>3.5099999999999998</v>
-      </c>
-      <c r="L10">
-        <v>94.799999999999997</v>
-      </c>
-      <c r="M10">
-        <v>1003</v>
-      </c>
-      <c r="N10">
-        <v>4.9900000000000002</v>
-      </c>
-      <c r="O10">
-        <v>14</v>
-      </c>
-      <c r="P10">
-        <v>960</v>
-      </c>
-      <c r="Q10">
-        <v>3.8799999999999999</v>
-      </c>
-      <c r="R10">
-        <v>16</v>
-      </c>
-      <c r="S10">
-        <v>713</v>
-      </c>
-      <c r="T10">
-        <v>5.46</v>
-      </c>
-      <c r="U10">
-        <v>4.7999999999999998</v>
-      </c>
-      <c r="V10">
-        <v>1110</v>
-      </c>
-      <c r="W10">
-        <v>4.4199999999999999</v>
-      </c>
-      <c r="X10">
-        <v>37.399999999999999</v>
-      </c>
-      <c r="Y10">
-        <v>1490</v>
-      </c>
-      <c r="Z10">
-        <v>5.4000000000000004</v>
-      </c>
-      <c r="AA10">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="AB10">
-        <v>622</v>
-      </c>
-      <c r="AC10">
-        <v>5.7800000000000002</v>
-      </c>
-      <c r="AD10">
-        <v>19.199999999999999</v>
-      </c>
-      <c r="AE10">
-        <v>847</v>
-      </c>
-      <c r="AF10">
-        <v>4.6299999999999999</v>
-      </c>
-      <c r="AG10">
-        <v>81.299999999999997</v>
-      </c>
-      <c r="AH10">
-        <v>669</v>
-      </c>
-      <c r="AI10">
-        <v>4.3300000000000001</v>
-      </c>
-      <c r="AJ10">
-        <v>69</v>
-      </c>
-    </row>
+    <row r="9" ht="12.75"/>
+    <row r="10" ht="12.75"/>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="M1:AA1"/>
-    <mergeCell ref="AB1:AJ1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="D2:F2"/>
-    <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="M2:O2"/>
-    <mergeCell ref="P2:R2"/>
-    <mergeCell ref="S2:U2"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="Y2:AA2"/>
-    <mergeCell ref="AB2:AD2"/>
-    <mergeCell ref="AE2:AG2"/>
-    <mergeCell ref="AH2:AJ2"/>
-  </mergeCells>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="300" verticalDpi="300" copies="1"/>
